--- a/flaskbackend/centercost_data/2025년6월.xlsx
+++ b/flaskbackend/centercost_data/2025년6월.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="271">
   <si>
     <t>코스트센터코드</t>
   </si>
@@ -827,9 +827,6 @@
   </si>
   <si>
     <t>(제)외주가공비-원자재</t>
-  </si>
-  <si>
-    <t>총비용</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E918"/>
+  <dimension ref="A1:E917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1289,7 +1286,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>844897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2037,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="E50">
-        <v>1033858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2632,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="E85">
-        <v>126334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3890,7 +3887,7 @@
         <v>189</v>
       </c>
       <c r="E159">
-        <v>1015313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4145,7 +4142,7 @@
         <v>189</v>
       </c>
       <c r="E174">
-        <v>150843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4434,7 +4431,7 @@
         <v>189</v>
       </c>
       <c r="E191">
-        <v>746649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4604,7 +4601,7 @@
         <v>189</v>
       </c>
       <c r="E201">
-        <v>2471703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4893,7 +4890,7 @@
         <v>189</v>
       </c>
       <c r="E218">
-        <v>549068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5471,7 +5468,7 @@
         <v>189</v>
       </c>
       <c r="E252">
-        <v>233863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -6049,7 +6046,7 @@
         <v>189</v>
       </c>
       <c r="E286">
-        <v>424277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6270,7 +6267,7 @@
         <v>189</v>
       </c>
       <c r="E299">
-        <v>503161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -6406,7 +6403,7 @@
         <v>189</v>
       </c>
       <c r="E307">
-        <v>1567860</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -6542,7 +6539,7 @@
         <v>189</v>
       </c>
       <c r="E315">
-        <v>683805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6661,7 +6658,7 @@
         <v>219</v>
       </c>
       <c r="E322">
-        <v>0</v>
+        <v>18819157</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6712,7 +6709,7 @@
         <v>189</v>
       </c>
       <c r="E325">
-        <v>1300587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6831,7 +6828,7 @@
         <v>189</v>
       </c>
       <c r="E332">
-        <v>219315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -7001,7 +6998,7 @@
         <v>189</v>
       </c>
       <c r="E342">
-        <v>276399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -7222,7 +7219,7 @@
         <v>189</v>
       </c>
       <c r="E355">
-        <v>3627097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -7749,7 +7746,7 @@
         <v>100</v>
       </c>
       <c r="E386">
-        <v>8009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -8038,7 +8035,7 @@
         <v>189</v>
       </c>
       <c r="E403">
-        <v>687718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -8157,7 +8154,7 @@
         <v>189</v>
       </c>
       <c r="E410">
-        <v>179186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -8225,7 +8222,7 @@
         <v>219</v>
       </c>
       <c r="E414">
-        <v>0</v>
+        <v>53071001</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -8276,7 +8273,7 @@
         <v>189</v>
       </c>
       <c r="E417">
-        <v>2109626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -8599,7 +8596,7 @@
         <v>189</v>
       </c>
       <c r="E436">
-        <v>411030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -9330,7 +9327,7 @@
         <v>100</v>
       </c>
       <c r="E479">
-        <v>264978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -10248,7 +10245,7 @@
         <v>100</v>
       </c>
       <c r="E533">
-        <v>336652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -10418,7 +10415,7 @@
         <v>100</v>
       </c>
       <c r="E543">
-        <v>381090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -10537,7 +10534,7 @@
         <v>100</v>
       </c>
       <c r="E550">
-        <v>266550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -10656,7 +10653,7 @@
         <v>189</v>
       </c>
       <c r="E557">
-        <v>173648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -10843,7 +10840,7 @@
         <v>189</v>
       </c>
       <c r="E568">
-        <v>330839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -11013,7 +11010,7 @@
         <v>189</v>
       </c>
       <c r="E578">
-        <v>86345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -11319,7 +11316,7 @@
         <v>189</v>
       </c>
       <c r="E596">
-        <v>1402658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -11472,7 +11469,7 @@
         <v>189</v>
       </c>
       <c r="E605">
-        <v>90277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -11710,7 +11707,7 @@
         <v>100</v>
       </c>
       <c r="E619">
-        <v>47433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -12407,7 +12404,7 @@
         <v>189</v>
       </c>
       <c r="E660">
-        <v>2232340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -12985,7 +12982,7 @@
         <v>189</v>
       </c>
       <c r="E694">
-        <v>206231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -13342,7 +13339,7 @@
         <v>189</v>
       </c>
       <c r="E715">
-        <v>1042131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716" spans="1:5">
@@ -13580,7 +13577,7 @@
         <v>189</v>
       </c>
       <c r="E729">
-        <v>259163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -13716,7 +13713,7 @@
         <v>189</v>
       </c>
       <c r="E737">
-        <v>1287293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -13835,7 +13832,7 @@
         <v>189</v>
       </c>
       <c r="E744">
-        <v>120381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -14124,7 +14121,7 @@
         <v>189</v>
       </c>
       <c r="E761">
-        <v>614152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -15586,7 +15583,7 @@
         <v>189</v>
       </c>
       <c r="E847">
-        <v>353905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848" spans="1:5">
@@ -16777,14 +16774,6 @@
       </c>
       <c r="E917">
         <v>17929307</v>
-      </c>
-    </row>
-    <row r="918" spans="1:5">
-      <c r="D918" t="s">
-        <v>271</v>
-      </c>
-      <c r="E918">
-        <v>13356014903</v>
       </c>
     </row>
   </sheetData>
